--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_i_peringr_median_a_2018.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_i_peringr_median_a_2018.xlsx
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:43</t>
+    <t xml:space="preserve">2026-09-24 00:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -693,7 +693,7 @@
         <v>0.36</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="15">
@@ -707,7 +707,7 @@
         <v>-0.04</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="16">
@@ -721,7 +721,7 @@
         <v>0.41</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="17">
@@ -735,7 +735,7 @@
         <v>0.32</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="18">

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_i_peringr_median_a_2018.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_i_peringr_median_a_2018.xlsx
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:33</t>
+    <t xml:space="preserve">2026-10-01 23:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_i_peringr_median_a_2018.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_i_peringr_median_a_2018.xlsx
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:04</t>
+    <t xml:space="preserve">2026-10-05 19:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
